--- a/output/pdf_financials_xlsx/ANK.xlsx
+++ b/output/pdf_financials_xlsx/ANK.xlsx
@@ -1222,16 +1222,16 @@
         <v>-1.73071</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.233876</v>
+        <v>-1.233876</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>5.685688</v>
+        <v>-5.685688</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>2.714981</v>
+        <v>-2.714981</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.99304</v>
+        <v>-0.99304</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>-0.6382100000000001</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3.702566</v>
+        <v>-3.702566</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3.068187</v>
+        <v>-3.068187</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-1.042546</v>
@@ -1490,16 +1490,16 @@
         <v>-1.73071</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.233876</v>
+        <v>-1.233876</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>5.685688</v>
+        <v>-5.685688</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>2.714981</v>
+        <v>-2.714981</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.99304</v>
+        <v>-0.99304</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>-0.6382100000000001</v>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3.702566</v>
+        <v>-3.702566</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>3.068187</v>
+        <v>-3.068187</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-1.042546</v>
@@ -1646,16 +1646,16 @@
         <v>-1.73071</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1.233876</v>
+        <v>-1.233876</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>5.685688</v>
+        <v>-5.685688</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>2.714981</v>
+        <v>-2.714981</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.99304</v>
+        <v>-0.99304</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>-0.6382100000000001</v>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>9.743594999999999</v>
+        <v>-9.743594999999999</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>61.36374</v>
+        <v>-61.36374</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-142.1422</v>
+        <v>142.1422</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-135.74905</v>
+        <v>135.74905</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -1874,16 +1874,16 @@
         <v>-1.73071</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.233876</v>
+        <v>-1.233876</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>5.685688</v>
+        <v>-5.685688</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>2.714981</v>
+        <v>-2.714981</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.99304</v>
+        <v>-0.99304</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-0.6382100000000001</v>
@@ -1978,16 +1978,16 @@
         <v>-1.73071</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.233876</v>
+        <v>-1.233876</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>5.685688</v>
+        <v>-5.685688</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>2.714981</v>
+        <v>-2.714981</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.99304</v>
+        <v>-0.99304</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-0.6382100000000001</v>
@@ -2112,16 +2112,16 @@
         <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>-0</v>
@@ -6646,19 +6646,19 @@
         <v>0.200894</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.384546</v>
+        <v>-1.70495</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-1.395796</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.659059</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.589448</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.597645</v>
       </c>
       <c r="N118" s="3" t="n">
         <v>-0.030509</v>
@@ -28438,7 +28438,11 @@
           <t>Exploration and evaluation expenditure (7)</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -34008,7 +34012,11 @@
           <t>Exploration and evaluation expenditure (9)</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -48512,10 +48520,10 @@
         </is>
       </c>
       <c r="Q455" s="5" t="n">
-        <v>0.99304</v>
+        <v>-0.99304</v>
       </c>
       <c r="R455" s="5" t="n">
-        <v>0.6382100000000001</v>
+        <v>-0.6382100000000001</v>
       </c>
       <c r="S455" t="inlineStr">
         <is>
@@ -48694,10 +48702,10 @@
         </is>
       </c>
       <c r="Q457" s="5" t="n">
-        <v>0.931211</v>
+        <v>-0.931211</v>
       </c>
       <c r="R457" s="5" t="n">
-        <v>0.451803</v>
+        <v>-0.451803</v>
       </c>
       <c r="S457" t="inlineStr">
         <is>
@@ -50386,10 +50394,10 @@
         </is>
       </c>
       <c r="P476" s="5" t="n">
-        <v>2.714981</v>
+        <v>-2.714981</v>
       </c>
       <c r="Q476" s="5" t="n">
-        <v>0.99304</v>
+        <v>-0.99304</v>
       </c>
       <c r="R476" t="inlineStr">
         <is>
@@ -50568,10 +50576,10 @@
         </is>
       </c>
       <c r="P478" s="5" t="n">
-        <v>2.651481</v>
+        <v>-2.651481</v>
       </c>
       <c r="Q478" s="5" t="n">
-        <v>0.931211</v>
+        <v>-0.931211</v>
       </c>
       <c r="R478" t="inlineStr">
         <is>
@@ -51729,13 +51737,13 @@
         </is>
       </c>
       <c r="N491" s="5" t="n">
-        <v>1.233876</v>
+        <v>-1.233876</v>
       </c>
       <c r="O491" s="5" t="n">
-        <v>5.685688</v>
+        <v>-5.685688</v>
       </c>
       <c r="P491" s="5" t="n">
-        <v>2.714981</v>
+        <v>-2.714981</v>
       </c>
       <c r="Q491" t="inlineStr">
         <is>
@@ -51914,10 +51922,10 @@
         </is>
       </c>
       <c r="O493" s="5" t="n">
-        <v>5.905588</v>
+        <v>-5.905588</v>
       </c>
       <c r="P493" s="5" t="n">
-        <v>2.778481</v>
+        <v>-2.778481</v>
       </c>
       <c r="Q493" t="inlineStr">
         <is>
@@ -52718,10 +52726,10 @@
         </is>
       </c>
       <c r="N502" s="5" t="n">
-        <v>1.014794</v>
+        <v>-1.014794</v>
       </c>
       <c r="O502" s="5" t="n">
-        <v>5.905588</v>
+        <v>-5.905588</v>
       </c>
       <c r="P502" t="inlineStr">
         <is>
@@ -63331,13 +63339,13 @@
         </is>
       </c>
       <c r="E620" s="5" t="n">
-        <v>3.702566</v>
+        <v>-3.702566</v>
       </c>
       <c r="F620" s="5" t="n">
-        <v>3.068187</v>
+        <v>-3.068187</v>
       </c>
       <c r="G620" s="5" t="n">
-        <v>1.034484</v>
+        <v>-1.034484</v>
       </c>
       <c r="H620" t="inlineStr">
         <is>
@@ -63511,13 +63519,13 @@
         </is>
       </c>
       <c r="E622" s="5" t="n">
-        <v>3.651057</v>
+        <v>-3.651057</v>
       </c>
       <c r="F622" s="5" t="n">
-        <v>3.097638</v>
+        <v>-3.097638</v>
       </c>
       <c r="G622" s="5" t="n">
-        <v>1.042546</v>
+        <v>-1.042546</v>
       </c>
       <c r="H622" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ANK.xlsx
+++ b/output/pdf_financials_xlsx/ANK.xlsx
@@ -2244,25 +2244,25 @@
         <v>0.886159</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.246396</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.645854</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.365326</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.586332</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.398224</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.60646</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.056723</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>0.169583</v>
@@ -2348,25 +2348,25 @@
         <v>0.886159</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.246396</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.645854</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.365326</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.586332</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.398224</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.60646</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.056723</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>0.169583</v>
@@ -2972,25 +2972,25 @@
         <v>0.008132</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.535482</v>
+        <v>0.289086</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.82691</v>
+        <v>0.181056</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.376492</v>
+        <v>0.011166</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.598799</v>
+        <v>0.012467</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.413951</v>
+        <v>0.015727</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.678416</v>
+        <v>0.07195600000000001</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.070226</v>
+        <v>0.013503</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0.014444</v>
@@ -9825,7 +9825,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">

--- a/output/pdf_financials_xlsx/ANK.xlsx
+++ b/output/pdf_financials_xlsx/ANK.xlsx
@@ -6349,7 +6349,7 @@
         <v>0</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.105983</v>
       </c>
       <c r="O112" s="3" t="n">
         <v>0</v>
@@ -27291,7 +27291,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -28620,7 +28624,11 @@
           <t>Proceeds on disposal of property and equipment (6)</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
